--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.61239340456358</v>
+        <v>7.574513928241581</v>
       </c>
       <c r="D2" t="n">
-        <v>46.09753793419466</v>
+        <v>7.490849914306633</v>
       </c>
       <c r="E2" t="n">
-        <v>7.365206812671719</v>
+        <v>1.196846107059154</v>
       </c>
       <c r="F2" t="n">
-        <v>8.084587403195568</v>
+        <v>1.31374545301928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.92305012885356</v>
+        <v>5.674995645938703</v>
       </c>
       <c r="D3" t="n">
-        <v>35.31462445742152</v>
+        <v>5.738626474330997</v>
       </c>
       <c r="E3" t="n">
-        <v>7.365206812671719</v>
+        <v>1.196846107059154</v>
       </c>
       <c r="F3" t="n">
-        <v>8.084587403195568</v>
+        <v>1.31374545301928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.66846382791535</v>
+        <v>8.558625372036245</v>
       </c>
       <c r="D4" t="n">
-        <v>55.0907630961459</v>
+        <v>8.952249003123709</v>
       </c>
       <c r="E4" t="n">
-        <v>7.365206812671719</v>
+        <v>1.196846107059154</v>
       </c>
       <c r="F4" t="n">
-        <v>8.084587403195568</v>
+        <v>1.31374545301928</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
